--- a/Python_2026/KPI_Measurement/JRCM_KPI_2026.xlsx
+++ b/Python_2026/KPI_Measurement/JRCM_KPI_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Development_2026\Python_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Development_2026\Python_2026\KPI_Measurement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D9CC4D-730E-4A7F-BE49-E0ACE02E2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A720DBAD-7214-4596-886E-3B5E729AC12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="645" windowWidth="25725" windowHeight="14235" xr2:uid="{11C83BD3-EFE0-40C3-BAD3-524289020AF7}"/>
+    <workbookView xWindow="2115" yWindow="270" windowWidth="26805" windowHeight="14730" xr2:uid="{11C83BD3-EFE0-40C3-BAD3-524289020AF7}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,79 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+  <pythonScripts>
+    <pythonScript>
+      <code>import pandas as pd
+# M값만 사용
+df = pd.DataFrame({
+    "M": [xl(%P2%)]
+})
+# Step 1: 구간 정의 (기존 C 기준 재활용)
+bins = [-1, 0, 2, 5, 9, 12, float('inf')]
+scores = [0, 0.5, 1, 1.5, 2, 2.5]
+# Step 2: Pandas cut으로 점수 매핑
+df["score"] = pd.cut(df["M"], bins=bins, labels=scores).astype(float)
+# 결과 반환
+df["score"].iloc[0]</code>
+    </pythonScript>
+  </pythonScripts>
+</python>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
@@ -84,42 +157,42 @@
   </si>
   <si>
     <t>May (Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>KPI</t>
   </si>
   <si>
     <t>Jun (Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>KPI</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Jul(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Aug(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Sep(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Oct(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Nov(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Dec(Count)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Jan (Count)</t>
@@ -135,7 +208,7 @@
   </si>
   <si>
     <t>Max</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Jan</t>
@@ -175,15 +248,15 @@
   </si>
   <si>
     <t>Total</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Case (Max 85 cases) - Target 0%</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Value (Max 16.5 point) - Target 100%</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>All achieved (100%): 0
@@ -224,20 +297,27 @@
   </si>
   <si>
     <t>Max count</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -399,6 +479,21 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="33">
@@ -713,136 +808,139 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -866,7 +964,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -875,17 +973,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="46">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="24" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="28" builtinId="38" customBuiltin="1"/>
@@ -917,16 +1015,19 @@
     <cellStyle name="Good" xfId="7" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="3" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 2 2" xfId="44" xr:uid="{9E1D0B7D-B649-4275-AB62-B6C049223724}"/>
     <cellStyle name="Heading 3" xfId="5" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="6" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Input" xfId="10" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="13" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="43" xr:uid="{DC34B27E-5D31-44E4-8DF0-18F0A354B658}"/>
     <cellStyle name="Note" xfId="16" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="11" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Title 2" xfId="45" xr:uid="{2B2F019E-53AC-4CAE-9815-658BE4DC8C26}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="15" builtinId="11" customBuiltin="1"/>
   </cellStyles>
@@ -1162,6 +1263,9 @@
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1312,6 +1416,9 @@
                   <c:v>0.87878787878787878</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -3519,16 +3626,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>136071</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>415419</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>326571</xdr:rowOff>
+      <xdr:rowOff>437829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>54429</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>68036</xdr:rowOff>
+      <xdr:rowOff>179294</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3554,6 +3661,93 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <fb>0</fb>
+    <v>&lt;class 'numpy.float64'&gt;</v>
+    <v>float64</v>
+    <v>0.0</v>
+    <v>0</v>
+    <v>0</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="basicValue"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbData count="1">
+    <spb s="0">
+      <v>https://www.anaconda.com/excel</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
+      <v>Python provided by Anaconda</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
+  <s>
+    <k n="link" t="s"/>
+    <k n="logo" t="s"/>
+    <k n="name" t="s"/>
+  </s>
+</spbStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3876,10 +4070,11 @@
   <dimension ref="A1:AB15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.5" style="12" customWidth="1"/>
+    <col min="1" max="1" width="29.5" style="10" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
     <col min="3" max="3" width="36.5" customWidth="1"/>
     <col min="4" max="12" width="9" style="2"/>
+    <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.3">
@@ -3919,10 +4114,10 @@
       <c r="L1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
       <c r="O1" s="4" t="s">
@@ -4005,6 +4200,13 @@
       <c r="L2" s="3">
         <v>0</v>
       </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" cm="1" vm="1">
+        <f t="array" ref="N2">_xlfn._xlws.PY(0,1,M2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
@@ -4043,6 +4245,13 @@
       <c r="L3" s="3">
         <v>0</v>
       </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" cm="1" vm="1">
+        <f t="array" ref="N3">_xlfn._xlws.PY(0,1,M3)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -4081,6 +4290,13 @@
       <c r="L4" s="3">
         <v>0</v>
       </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" cm="1" vm="1">
+        <f t="array" ref="N4">_xlfn._xlws.PY(0,1,M4)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -4119,6 +4335,13 @@
       <c r="L5" s="3">
         <v>0</v>
       </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" cm="1" vm="1">
+        <f t="array" ref="N5">_xlfn._xlws.PY(0,1,M5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -4157,6 +4380,13 @@
       <c r="L6" s="3">
         <v>0</v>
       </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" cm="1" vm="1">
+        <f t="array" ref="N6">_xlfn._xlws.PY(0,1,M6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -4195,6 +4425,13 @@
       <c r="L7" s="3">
         <v>0</v>
       </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" cm="1" vm="1">
+        <f t="array" ref="N7">_xlfn._xlws.PY(0,1,M7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:28" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
@@ -4233,6 +4470,13 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" cm="1" vm="1">
+        <f t="array" ref="N8">_xlfn._xlws.PY(0,1,M8)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:28" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
@@ -4269,6 +4513,13 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" cm="1" vm="1">
+        <f t="array" ref="N9">_xlfn._xlws.PY(0,1,M9)</f>
         <v>0</v>
       </c>
     </row>
@@ -4284,7 +4535,7 @@
         <v>16.5</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" ref="E10:L10" si="0">SUM(E2:E9)</f>
+        <f t="shared" ref="E10:N10" si="0">SUM(E2:E9)</f>
         <v>4</v>
       </c>
       <c r="F10" s="3">
@@ -4312,6 +4563,14 @@
         <v>0</v>
       </c>
       <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4350,12 +4609,20 @@
         <f>1-(L10/$D$10)</f>
         <v>1</v>
       </c>
+      <c r="M11" s="6">
+        <f>(M10/$C$10)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <f>1-(N10/$D$10)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="E13" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10"/>
+      <c r="E13" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="7" t="s">
         <v>29</v>
       </c>
@@ -4397,10 +4664,10 @@
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="6">
         <f>(E10/$C$10)</f>
         <v>4.878048780487805E-2</v>
@@ -4417,7 +4684,10 @@
         <f>(K10/$C$10)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="6"/>
+      <c r="K14" s="6">
+        <f>(L10/$C$10)</f>
+        <v>0</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
@@ -4427,14 +4697,14 @@
       <c r="R14" s="5"/>
       <c r="S14" s="8">
         <f>AVERAGE(G14:R14)</f>
-        <v>3.048780487804878E-2</v>
+        <v>2.4390243902439025E-2</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="6">
         <f>F11</f>
         <v>0.93939393939393945</v>
@@ -4451,7 +4721,10 @@
         <f>L11</f>
         <v>1</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="6">
+        <f>N11</f>
+        <v>1</v>
+      </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
@@ -4461,7 +4734,7 @@
       <c r="R15" s="5"/>
       <c r="S15" s="8">
         <f>AVERAGE(G15:R15)</f>
-        <v>0.95454545454545459</v>
+        <v>0.96363636363636362</v>
       </c>
     </row>
   </sheetData>
@@ -4470,7 +4743,7 @@
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
